--- a/artfynd/A 4107-2022 artfynd.xlsx
+++ b/artfynd/A 4107-2022 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>127299641</v>
       </c>
       <c r="B3" t="n">
-        <v>91337</v>
+        <v>91343</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>127299648</v>
       </c>
       <c r="B4" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -971,32 +971,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127299653</v>
+        <v>127299646</v>
       </c>
       <c r="B5" t="n">
-        <v>5176</v>
+        <v>79014</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>861798</v>
+        <v>861776</v>
       </c>
       <c r="R5" t="n">
-        <v>7457305</v>
+        <v>7457178</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1042,11 +1042,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1073,10 +1068,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127299646</v>
+        <v>127299643</v>
       </c>
       <c r="B6" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1108,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>861776</v>
+        <v>861770</v>
       </c>
       <c r="R6" t="n">
-        <v>7457178</v>
+        <v>7457108</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1170,10 +1165,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127299643</v>
+        <v>127299647</v>
       </c>
       <c r="B7" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1205,10 +1200,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>861770</v>
+        <v>861844</v>
       </c>
       <c r="R7" t="n">
-        <v>7457108</v>
+        <v>7457403</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1267,32 +1262,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127299647</v>
+        <v>127299653</v>
       </c>
       <c r="B8" t="n">
-        <v>79011</v>
+        <v>5176</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1302,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>861844</v>
+        <v>861798</v>
       </c>
       <c r="R8" t="n">
-        <v>7457403</v>
+        <v>7457305</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1338,6 +1333,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1469,7 +1469,7 @@
         <v>127299622</v>
       </c>
       <c r="B10" t="n">
-        <v>105456</v>
+        <v>105462</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1563,32 +1563,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127299626</v>
+        <v>127299627</v>
       </c>
       <c r="B11" t="n">
-        <v>91284</v>
+        <v>57817</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5447</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1598,10 +1598,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>861728</v>
+        <v>861840</v>
       </c>
       <c r="R11" t="n">
-        <v>7457083</v>
+        <v>7457419</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1660,32 +1660,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127299627</v>
+        <v>127299626</v>
       </c>
       <c r="B12" t="n">
-        <v>57817</v>
+        <v>91290</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1695,10 +1695,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>861840</v>
+        <v>861728</v>
       </c>
       <c r="R12" t="n">
-        <v>7457419</v>
+        <v>7457083</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1760,7 +1760,7 @@
         <v>127299642</v>
       </c>
       <c r="B13" t="n">
-        <v>91337</v>
+        <v>91343</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1857,7 +1857,7 @@
         <v>127299629</v>
       </c>
       <c r="B14" t="n">
-        <v>97314</v>
+        <v>97320</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1954,7 +1954,7 @@
         <v>127299649</v>
       </c>
       <c r="B15" t="n">
-        <v>98353</v>
+        <v>98359</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2051,7 +2051,7 @@
         <v>127299644</v>
       </c>
       <c r="B16" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2148,7 +2148,7 @@
         <v>127299625</v>
       </c>
       <c r="B17" t="n">
-        <v>75135</v>
+        <v>75138</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2245,7 +2245,7 @@
         <v>127299640</v>
       </c>
       <c r="B18" t="n">
-        <v>91315</v>
+        <v>91321</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2436,32 +2436,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127299631</v>
+        <v>127299645</v>
       </c>
       <c r="B20" t="n">
-        <v>97314</v>
+        <v>79014</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2471,10 +2471,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>861925</v>
+        <v>861782</v>
       </c>
       <c r="R20" t="n">
-        <v>7457463</v>
+        <v>7457172</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2533,32 +2533,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127299645</v>
+        <v>127299631</v>
       </c>
       <c r="B21" t="n">
-        <v>79011</v>
+        <v>97320</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2568,10 +2568,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>861782</v>
+        <v>861925</v>
       </c>
       <c r="R21" t="n">
-        <v>7457172</v>
+        <v>7457463</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>

--- a/artfynd/A 4107-2022 artfynd.xlsx
+++ b/artfynd/A 4107-2022 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127299641</v>
+        <v>127299648</v>
       </c>
       <c r="B3" t="n">
-        <v>91343</v>
+        <v>79014</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,21 +788,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>861760</v>
+        <v>861927</v>
       </c>
       <c r="R3" t="n">
-        <v>7457133</v>
+        <v>7457463</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -874,10 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127299648</v>
+        <v>127299641</v>
       </c>
       <c r="B4" t="n">
-        <v>79014</v>
+        <v>91343</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -885,21 +885,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>861927</v>
+        <v>861760</v>
       </c>
       <c r="R4" t="n">
-        <v>7457463</v>
+        <v>7457133</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -971,10 +971,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127299646</v>
+        <v>127299638</v>
       </c>
       <c r="B5" t="n">
-        <v>79014</v>
+        <v>56840</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -982,21 +982,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>861776</v>
+        <v>861780</v>
       </c>
       <c r="R5" t="n">
-        <v>7457178</v>
+        <v>7457155</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1042,6 +1042,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Upprörd, varnande</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1068,7 +1073,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127299643</v>
+        <v>127299646</v>
       </c>
       <c r="B6" t="n">
         <v>79014</v>
@@ -1103,10 +1108,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>861770</v>
+        <v>861776</v>
       </c>
       <c r="R6" t="n">
-        <v>7457108</v>
+        <v>7457178</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1165,7 +1170,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127299647</v>
+        <v>127299643</v>
       </c>
       <c r="B7" t="n">
         <v>79014</v>
@@ -1200,10 +1205,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>861844</v>
+        <v>861770</v>
       </c>
       <c r="R7" t="n">
-        <v>7457403</v>
+        <v>7457108</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1262,32 +1267,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127299653</v>
+        <v>127299647</v>
       </c>
       <c r="B8" t="n">
-        <v>5176</v>
+        <v>79014</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1297,10 +1302,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>861798</v>
+        <v>861844</v>
       </c>
       <c r="R8" t="n">
-        <v>7457305</v>
+        <v>7457403</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1333,11 +1338,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1364,32 +1364,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127299638</v>
+        <v>127299653</v>
       </c>
       <c r="B9" t="n">
-        <v>56840</v>
+        <v>5176</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102612</v>
+        <v>100526</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1399,10 +1399,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>861780</v>
+        <v>861798</v>
       </c>
       <c r="R9" t="n">
-        <v>7457155</v>
+        <v>7457305</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1439,7 +1439,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Upprörd, varnande</t>
+          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -2533,10 +2533,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127299631</v>
+        <v>127299652</v>
       </c>
       <c r="B21" t="n">
-        <v>97320</v>
+        <v>5176</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2544,21 +2544,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221945</v>
+        <v>100526</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2568,10 +2568,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>861925</v>
+        <v>861748</v>
       </c>
       <c r="R21" t="n">
-        <v>7457463</v>
+        <v>7457109</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2604,6 +2604,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2630,10 +2635,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127299652</v>
+        <v>127299631</v>
       </c>
       <c r="B22" t="n">
-        <v>5176</v>
+        <v>97320</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2641,21 +2646,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100526</v>
+        <v>221945</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2665,10 +2670,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>861748</v>
+        <v>861925</v>
       </c>
       <c r="R22" t="n">
-        <v>7457109</v>
+        <v>7457463</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2701,11 +2706,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD22" t="b">

--- a/artfynd/A 4107-2022 artfynd.xlsx
+++ b/artfynd/A 4107-2022 artfynd.xlsx
@@ -1563,32 +1563,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127299627</v>
+        <v>127299626</v>
       </c>
       <c r="B11" t="n">
-        <v>57817</v>
+        <v>91290</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>5447</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1598,10 +1598,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>861840</v>
+        <v>861728</v>
       </c>
       <c r="R11" t="n">
-        <v>7457419</v>
+        <v>7457083</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1660,32 +1660,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127299626</v>
+        <v>127299627</v>
       </c>
       <c r="B12" t="n">
-        <v>91290</v>
+        <v>57817</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5447</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1695,10 +1695,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>861728</v>
+        <v>861840</v>
       </c>
       <c r="R12" t="n">
-        <v>7457083</v>
+        <v>7457419</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>

--- a/artfynd/A 4107-2022 artfynd.xlsx
+++ b/artfynd/A 4107-2022 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127299648</v>
+        <v>127299641</v>
       </c>
       <c r="B3" t="n">
-        <v>79014</v>
+        <v>91344</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,21 +788,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>861927</v>
+        <v>861760</v>
       </c>
       <c r="R3" t="n">
-        <v>7457463</v>
+        <v>7457133</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -874,10 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127299641</v>
+        <v>127299648</v>
       </c>
       <c r="B4" t="n">
-        <v>91343</v>
+        <v>79014</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -885,21 +885,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>861760</v>
+        <v>861927</v>
       </c>
       <c r="R4" t="n">
-        <v>7457133</v>
+        <v>7457463</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -971,10 +971,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127299638</v>
+        <v>127299646</v>
       </c>
       <c r="B5" t="n">
-        <v>56840</v>
+        <v>79014</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -982,21 +982,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>861780</v>
+        <v>861776</v>
       </c>
       <c r="R5" t="n">
-        <v>7457155</v>
+        <v>7457178</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1042,11 +1042,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Upprörd, varnande</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1073,7 +1068,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127299646</v>
+        <v>127299643</v>
       </c>
       <c r="B6" t="n">
         <v>79014</v>
@@ -1108,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>861776</v>
+        <v>861770</v>
       </c>
       <c r="R6" t="n">
-        <v>7457178</v>
+        <v>7457108</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1170,7 +1165,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127299643</v>
+        <v>127299647</v>
       </c>
       <c r="B7" t="n">
         <v>79014</v>
@@ -1205,10 +1200,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>861770</v>
+        <v>861844</v>
       </c>
       <c r="R7" t="n">
-        <v>7457108</v>
+        <v>7457403</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1267,10 +1262,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127299647</v>
+        <v>127299638</v>
       </c>
       <c r="B8" t="n">
-        <v>79014</v>
+        <v>56840</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1278,21 +1273,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1302,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>861844</v>
+        <v>861780</v>
       </c>
       <c r="R8" t="n">
-        <v>7457403</v>
+        <v>7457155</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1338,6 +1333,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Upprörd, varnande</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1469,7 +1469,7 @@
         <v>127299622</v>
       </c>
       <c r="B10" t="n">
-        <v>105462</v>
+        <v>105463</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>127299626</v>
       </c>
       <c r="B11" t="n">
-        <v>91290</v>
+        <v>91291</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1757,32 +1757,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127299642</v>
+        <v>127299629</v>
       </c>
       <c r="B13" t="n">
-        <v>91343</v>
+        <v>97321</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>221945</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1792,10 +1792,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>861728</v>
+        <v>861780</v>
       </c>
       <c r="R13" t="n">
-        <v>7457085</v>
+        <v>7457147</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1854,32 +1854,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127299629</v>
+        <v>127299642</v>
       </c>
       <c r="B14" t="n">
-        <v>97320</v>
+        <v>91344</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221945</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1889,10 +1889,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>861780</v>
+        <v>861728</v>
       </c>
       <c r="R14" t="n">
-        <v>7457147</v>
+        <v>7457085</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -1954,7 +1954,7 @@
         <v>127299649</v>
       </c>
       <c r="B15" t="n">
-        <v>98359</v>
+        <v>98360</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2245,7 +2245,7 @@
         <v>127299640</v>
       </c>
       <c r="B18" t="n">
-        <v>91321</v>
+        <v>91322</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2638,7 +2638,7 @@
         <v>127299631</v>
       </c>
       <c r="B22" t="n">
-        <v>97320</v>
+        <v>97321</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 4107-2022 artfynd.xlsx
+++ b/artfynd/A 4107-2022 artfynd.xlsx
@@ -1262,32 +1262,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127299638</v>
+        <v>127299653</v>
       </c>
       <c r="B8" t="n">
-        <v>56840</v>
+        <v>5176</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102612</v>
+        <v>100526</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>861780</v>
+        <v>861798</v>
       </c>
       <c r="R8" t="n">
-        <v>7457155</v>
+        <v>7457305</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Upprörd, varnande</t>
+          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1364,32 +1364,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127299653</v>
+        <v>127299638</v>
       </c>
       <c r="B9" t="n">
-        <v>5176</v>
+        <v>56840</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100526</v>
+        <v>102612</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1399,10 +1399,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>861798</v>
+        <v>861780</v>
       </c>
       <c r="R9" t="n">
-        <v>7457305</v>
+        <v>7457155</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1439,7 +1439,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Gnaggångar och kläckhål</t>
+          <t>Upprörd, varnande</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1563,32 +1563,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127299626</v>
+        <v>127299627</v>
       </c>
       <c r="B11" t="n">
-        <v>91291</v>
+        <v>57817</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5447</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1598,10 +1598,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>861728</v>
+        <v>861840</v>
       </c>
       <c r="R11" t="n">
-        <v>7457083</v>
+        <v>7457419</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1660,32 +1660,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127299627</v>
+        <v>127299626</v>
       </c>
       <c r="B12" t="n">
-        <v>57817</v>
+        <v>91291</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1695,10 +1695,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>861840</v>
+        <v>861728</v>
       </c>
       <c r="R12" t="n">
-        <v>7457419</v>
+        <v>7457083</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>

--- a/artfynd/A 4107-2022 artfynd.xlsx
+++ b/artfynd/A 4107-2022 artfynd.xlsx
@@ -1262,32 +1262,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127299653</v>
+        <v>127299638</v>
       </c>
       <c r="B8" t="n">
-        <v>5176</v>
+        <v>56840</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100526</v>
+        <v>102612</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>861798</v>
+        <v>861780</v>
       </c>
       <c r="R8" t="n">
-        <v>7457305</v>
+        <v>7457155</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Gnaggångar och kläckhål</t>
+          <t>Upprörd, varnande</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1364,32 +1364,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127299638</v>
+        <v>127299653</v>
       </c>
       <c r="B9" t="n">
-        <v>56840</v>
+        <v>5176</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102612</v>
+        <v>100526</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1399,10 +1399,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>861780</v>
+        <v>861798</v>
       </c>
       <c r="R9" t="n">
-        <v>7457155</v>
+        <v>7457305</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1439,7 +1439,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Upprörd, varnande</t>
+          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1757,32 +1757,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127299629</v>
+        <v>127299642</v>
       </c>
       <c r="B13" t="n">
-        <v>97321</v>
+        <v>91344</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221945</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1792,10 +1792,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>861780</v>
+        <v>861728</v>
       </c>
       <c r="R13" t="n">
-        <v>7457147</v>
+        <v>7457085</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1854,32 +1854,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127299642</v>
+        <v>127299629</v>
       </c>
       <c r="B14" t="n">
-        <v>91344</v>
+        <v>97321</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>221945</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1889,10 +1889,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>861728</v>
+        <v>861780</v>
       </c>
       <c r="R14" t="n">
-        <v>7457085</v>
+        <v>7457147</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>

--- a/artfynd/A 4107-2022 artfynd.xlsx
+++ b/artfynd/A 4107-2022 artfynd.xlsx
@@ -971,10 +971,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127299646</v>
+        <v>127299638</v>
       </c>
       <c r="B5" t="n">
-        <v>79014</v>
+        <v>56840</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -982,21 +982,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>861776</v>
+        <v>861780</v>
       </c>
       <c r="R5" t="n">
-        <v>7457178</v>
+        <v>7457155</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1042,6 +1042,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Upprörd, varnande</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1068,32 +1073,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127299643</v>
+        <v>127299653</v>
       </c>
       <c r="B6" t="n">
-        <v>79014</v>
+        <v>5176</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1103,10 +1108,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>861770</v>
+        <v>861798</v>
       </c>
       <c r="R6" t="n">
-        <v>7457108</v>
+        <v>7457305</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1139,6 +1144,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1165,7 +1175,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127299647</v>
+        <v>127299646</v>
       </c>
       <c r="B7" t="n">
         <v>79014</v>
@@ -1200,10 +1210,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>861844</v>
+        <v>861776</v>
       </c>
       <c r="R7" t="n">
-        <v>7457403</v>
+        <v>7457178</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1262,10 +1272,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127299638</v>
+        <v>127299643</v>
       </c>
       <c r="B8" t="n">
-        <v>56840</v>
+        <v>79014</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1273,21 +1283,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1297,10 +1307,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>861780</v>
+        <v>861770</v>
       </c>
       <c r="R8" t="n">
-        <v>7457155</v>
+        <v>7457108</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1333,11 +1343,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Upprörd, varnande</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1364,32 +1369,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127299653</v>
+        <v>127299647</v>
       </c>
       <c r="B9" t="n">
-        <v>5176</v>
+        <v>79014</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1399,10 +1404,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>861798</v>
+        <v>861844</v>
       </c>
       <c r="R9" t="n">
-        <v>7457305</v>
+        <v>7457403</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1435,11 +1440,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 4107-2022 artfynd.xlsx
+++ b/artfynd/A 4107-2022 artfynd.xlsx
@@ -971,10 +971,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127299638</v>
+        <v>127299646</v>
       </c>
       <c r="B5" t="n">
-        <v>56840</v>
+        <v>79014</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -982,21 +982,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>861780</v>
+        <v>861776</v>
       </c>
       <c r="R5" t="n">
-        <v>7457155</v>
+        <v>7457178</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1042,11 +1042,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Upprörd, varnande</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1073,32 +1068,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127299653</v>
+        <v>127299643</v>
       </c>
       <c r="B6" t="n">
-        <v>5176</v>
+        <v>79014</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1108,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>861798</v>
+        <v>861770</v>
       </c>
       <c r="R6" t="n">
-        <v>7457305</v>
+        <v>7457108</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1144,11 +1139,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1175,7 +1165,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127299646</v>
+        <v>127299647</v>
       </c>
       <c r="B7" t="n">
         <v>79014</v>
@@ -1210,10 +1200,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>861776</v>
+        <v>861844</v>
       </c>
       <c r="R7" t="n">
-        <v>7457178</v>
+        <v>7457403</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1272,10 +1262,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127299643</v>
+        <v>127299638</v>
       </c>
       <c r="B8" t="n">
-        <v>79014</v>
+        <v>56840</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1283,21 +1273,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1307,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>861770</v>
+        <v>861780</v>
       </c>
       <c r="R8" t="n">
-        <v>7457108</v>
+        <v>7457155</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1343,6 +1333,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Upprörd, varnande</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1369,32 +1364,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127299647</v>
+        <v>127299653</v>
       </c>
       <c r="B9" t="n">
-        <v>79014</v>
+        <v>5176</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1404,10 +1399,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>861844</v>
+        <v>861798</v>
       </c>
       <c r="R9" t="n">
-        <v>7457403</v>
+        <v>7457305</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1440,6 +1435,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1757,32 +1757,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127299642</v>
+        <v>127299629</v>
       </c>
       <c r="B13" t="n">
-        <v>91344</v>
+        <v>97321</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>221945</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1792,10 +1792,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>861728</v>
+        <v>861780</v>
       </c>
       <c r="R13" t="n">
-        <v>7457085</v>
+        <v>7457147</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1854,32 +1854,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127299629</v>
+        <v>127299642</v>
       </c>
       <c r="B14" t="n">
-        <v>97321</v>
+        <v>91344</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221945</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1889,10 +1889,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>861780</v>
+        <v>861728</v>
       </c>
       <c r="R14" t="n">
-        <v>7457147</v>
+        <v>7457085</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>

--- a/artfynd/A 4107-2022 artfynd.xlsx
+++ b/artfynd/A 4107-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127299623</v>
       </c>
       <c r="B2" t="n">
-        <v>5196</v>
+        <v>5197</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>127299641</v>
       </c>
       <c r="B3" t="n">
-        <v>91344</v>
+        <v>91348</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>127299648</v>
       </c>
       <c r="B4" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -971,32 +971,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127299646</v>
+        <v>127299653</v>
       </c>
       <c r="B5" t="n">
-        <v>79014</v>
+        <v>5177</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>861776</v>
+        <v>861798</v>
       </c>
       <c r="R5" t="n">
-        <v>7457178</v>
+        <v>7457305</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1042,6 +1042,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1068,10 +1073,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127299643</v>
+        <v>127299646</v>
       </c>
       <c r="B6" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1103,10 +1108,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>861770</v>
+        <v>861776</v>
       </c>
       <c r="R6" t="n">
-        <v>7457108</v>
+        <v>7457178</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1165,10 +1170,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127299647</v>
+        <v>127299643</v>
       </c>
       <c r="B7" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1200,10 +1205,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>861844</v>
+        <v>861770</v>
       </c>
       <c r="R7" t="n">
-        <v>7457403</v>
+        <v>7457108</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1262,10 +1267,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127299638</v>
+        <v>127299647</v>
       </c>
       <c r="B8" t="n">
-        <v>56840</v>
+        <v>79018</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1273,21 +1278,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1297,10 +1302,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>861780</v>
+        <v>861844</v>
       </c>
       <c r="R8" t="n">
-        <v>7457155</v>
+        <v>7457403</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1333,11 +1338,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Upprörd, varnande</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1364,32 +1364,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127299653</v>
+        <v>127299638</v>
       </c>
       <c r="B9" t="n">
-        <v>5176</v>
+        <v>56844</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100526</v>
+        <v>102612</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1399,10 +1399,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>861798</v>
+        <v>861780</v>
       </c>
       <c r="R9" t="n">
-        <v>7457305</v>
+        <v>7457155</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1439,7 +1439,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Gnaggångar och kläckhål</t>
+          <t>Upprörd, varnande</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1469,7 +1469,7 @@
         <v>127299622</v>
       </c>
       <c r="B10" t="n">
-        <v>105463</v>
+        <v>105469</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1563,32 +1563,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127299627</v>
+        <v>127299626</v>
       </c>
       <c r="B11" t="n">
-        <v>57817</v>
+        <v>91295</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>5447</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1598,10 +1598,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>861840</v>
+        <v>861728</v>
       </c>
       <c r="R11" t="n">
-        <v>7457419</v>
+        <v>7457083</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1660,32 +1660,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127299626</v>
+        <v>127299627</v>
       </c>
       <c r="B12" t="n">
-        <v>91291</v>
+        <v>57821</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5447</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1695,10 +1695,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>861728</v>
+        <v>861840</v>
       </c>
       <c r="R12" t="n">
-        <v>7457083</v>
+        <v>7457419</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1757,32 +1757,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127299629</v>
+        <v>127299642</v>
       </c>
       <c r="B13" t="n">
-        <v>97321</v>
+        <v>91348</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221945</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1792,10 +1792,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>861780</v>
+        <v>861728</v>
       </c>
       <c r="R13" t="n">
-        <v>7457147</v>
+        <v>7457085</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1854,32 +1854,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127299642</v>
+        <v>127299629</v>
       </c>
       <c r="B14" t="n">
-        <v>91344</v>
+        <v>97325</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>221945</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1889,10 +1889,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>861728</v>
+        <v>861780</v>
       </c>
       <c r="R14" t="n">
-        <v>7457085</v>
+        <v>7457147</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -1954,7 +1954,7 @@
         <v>127299649</v>
       </c>
       <c r="B15" t="n">
-        <v>98360</v>
+        <v>98364</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2051,7 +2051,7 @@
         <v>127299644</v>
       </c>
       <c r="B16" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2148,7 +2148,7 @@
         <v>127299625</v>
       </c>
       <c r="B17" t="n">
-        <v>75138</v>
+        <v>75142</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2245,7 +2245,7 @@
         <v>127299640</v>
       </c>
       <c r="B18" t="n">
-        <v>91322</v>
+        <v>91326</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2342,7 +2342,7 @@
         <v>127299628</v>
       </c>
       <c r="B19" t="n">
-        <v>57817</v>
+        <v>57821</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2439,7 +2439,7 @@
         <v>127299645</v>
       </c>
       <c r="B20" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2536,7 +2536,7 @@
         <v>127299652</v>
       </c>
       <c r="B21" t="n">
-        <v>5176</v>
+        <v>5177</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2638,7 +2638,7 @@
         <v>127299631</v>
       </c>
       <c r="B22" t="n">
-        <v>97321</v>
+        <v>97325</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 4107-2022 artfynd.xlsx
+++ b/artfynd/A 4107-2022 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127299641</v>
+        <v>127299648</v>
       </c>
       <c r="B3" t="n">
-        <v>91348</v>
+        <v>79018</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,21 +788,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>861760</v>
+        <v>861927</v>
       </c>
       <c r="R3" t="n">
-        <v>7457133</v>
+        <v>7457463</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -874,10 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127299648</v>
+        <v>127299641</v>
       </c>
       <c r="B4" t="n">
-        <v>79018</v>
+        <v>91348</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -885,21 +885,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>861927</v>
+        <v>861760</v>
       </c>
       <c r="R4" t="n">
-        <v>7457463</v>
+        <v>7457133</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -971,32 +971,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127299653</v>
+        <v>127299646</v>
       </c>
       <c r="B5" t="n">
-        <v>5177</v>
+        <v>79018</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>861798</v>
+        <v>861776</v>
       </c>
       <c r="R5" t="n">
-        <v>7457305</v>
+        <v>7457178</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1042,11 +1042,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1073,7 +1068,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127299646</v>
+        <v>127299643</v>
       </c>
       <c r="B6" t="n">
         <v>79018</v>
@@ -1108,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>861776</v>
+        <v>861770</v>
       </c>
       <c r="R6" t="n">
-        <v>7457178</v>
+        <v>7457108</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1170,7 +1165,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127299643</v>
+        <v>127299647</v>
       </c>
       <c r="B7" t="n">
         <v>79018</v>
@@ -1205,10 +1200,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>861770</v>
+        <v>861844</v>
       </c>
       <c r="R7" t="n">
-        <v>7457108</v>
+        <v>7457403</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1267,32 +1262,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127299647</v>
+        <v>127299653</v>
       </c>
       <c r="B8" t="n">
-        <v>79018</v>
+        <v>5177</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1302,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>861844</v>
+        <v>861798</v>
       </c>
       <c r="R8" t="n">
-        <v>7457403</v>
+        <v>7457305</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1338,6 +1333,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 4107-2022 artfynd.xlsx
+++ b/artfynd/A 4107-2022 artfynd.xlsx
@@ -971,10 +971,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127299646</v>
+        <v>127299638</v>
       </c>
       <c r="B5" t="n">
-        <v>79018</v>
+        <v>56844</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -982,21 +982,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>861776</v>
+        <v>861780</v>
       </c>
       <c r="R5" t="n">
-        <v>7457178</v>
+        <v>7457155</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1042,6 +1042,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Upprörd, varnande</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1068,7 +1073,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127299643</v>
+        <v>127299646</v>
       </c>
       <c r="B6" t="n">
         <v>79018</v>
@@ -1103,10 +1108,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>861770</v>
+        <v>861776</v>
       </c>
       <c r="R6" t="n">
-        <v>7457108</v>
+        <v>7457178</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1165,7 +1170,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127299647</v>
+        <v>127299643</v>
       </c>
       <c r="B7" t="n">
         <v>79018</v>
@@ -1200,10 +1205,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>861844</v>
+        <v>861770</v>
       </c>
       <c r="R7" t="n">
-        <v>7457403</v>
+        <v>7457108</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1262,32 +1267,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127299653</v>
+        <v>127299647</v>
       </c>
       <c r="B8" t="n">
-        <v>5177</v>
+        <v>79018</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1297,10 +1302,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>861798</v>
+        <v>861844</v>
       </c>
       <c r="R8" t="n">
-        <v>7457305</v>
+        <v>7457403</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1333,11 +1338,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1364,32 +1364,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127299638</v>
+        <v>127299653</v>
       </c>
       <c r="B9" t="n">
-        <v>56844</v>
+        <v>5177</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102612</v>
+        <v>100526</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1399,10 +1399,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>861780</v>
+        <v>861798</v>
       </c>
       <c r="R9" t="n">
-        <v>7457155</v>
+        <v>7457305</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1439,7 +1439,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Upprörd, varnande</t>
+          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1563,32 +1563,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127299626</v>
+        <v>127299627</v>
       </c>
       <c r="B11" t="n">
-        <v>91295</v>
+        <v>57821</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5447</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1598,10 +1598,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>861728</v>
+        <v>861840</v>
       </c>
       <c r="R11" t="n">
-        <v>7457083</v>
+        <v>7457419</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1660,32 +1660,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127299627</v>
+        <v>127299626</v>
       </c>
       <c r="B12" t="n">
-        <v>57821</v>
+        <v>91295</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1695,10 +1695,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>861840</v>
+        <v>861728</v>
       </c>
       <c r="R12" t="n">
-        <v>7457419</v>
+        <v>7457083</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>

--- a/artfynd/A 4107-2022 artfynd.xlsx
+++ b/artfynd/A 4107-2022 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127299648</v>
+        <v>127299641</v>
       </c>
       <c r="B3" t="n">
-        <v>79018</v>
+        <v>91348</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,21 +788,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>861927</v>
+        <v>861760</v>
       </c>
       <c r="R3" t="n">
-        <v>7457463</v>
+        <v>7457133</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -874,10 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127299641</v>
+        <v>127299648</v>
       </c>
       <c r="B4" t="n">
-        <v>91348</v>
+        <v>79018</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -885,21 +885,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>861760</v>
+        <v>861927</v>
       </c>
       <c r="R4" t="n">
-        <v>7457133</v>
+        <v>7457463</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -971,32 +971,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127299638</v>
+        <v>127299653</v>
       </c>
       <c r="B5" t="n">
-        <v>56844</v>
+        <v>5177</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102612</v>
+        <v>100526</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>861780</v>
+        <v>861798</v>
       </c>
       <c r="R5" t="n">
-        <v>7457155</v>
+        <v>7457305</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1046,7 +1046,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Upprörd, varnande</t>
+          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1364,32 +1364,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127299653</v>
+        <v>127299638</v>
       </c>
       <c r="B9" t="n">
-        <v>5177</v>
+        <v>56844</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100526</v>
+        <v>102612</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1399,10 +1399,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>861798</v>
+        <v>861780</v>
       </c>
       <c r="R9" t="n">
-        <v>7457305</v>
+        <v>7457155</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1439,7 +1439,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Gnaggångar och kläckhål</t>
+          <t>Upprörd, varnande</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1469,7 +1469,7 @@
         <v>127299622</v>
       </c>
       <c r="B10" t="n">
-        <v>105469</v>
+        <v>105471</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1563,32 +1563,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127299627</v>
+        <v>127299626</v>
       </c>
       <c r="B11" t="n">
-        <v>57821</v>
+        <v>91295</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>5447</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1598,10 +1598,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>861840</v>
+        <v>861728</v>
       </c>
       <c r="R11" t="n">
-        <v>7457419</v>
+        <v>7457083</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1660,32 +1660,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127299626</v>
+        <v>127299627</v>
       </c>
       <c r="B12" t="n">
-        <v>91295</v>
+        <v>57821</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5447</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1695,10 +1695,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>861728</v>
+        <v>861840</v>
       </c>
       <c r="R12" t="n">
-        <v>7457083</v>
+        <v>7457419</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1954,7 +1954,7 @@
         <v>127299649</v>
       </c>
       <c r="B15" t="n">
-        <v>98364</v>
+        <v>98365</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2242,10 +2242,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127299640</v>
+        <v>127299628</v>
       </c>
       <c r="B18" t="n">
-        <v>91326</v>
+        <v>57821</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2253,21 +2253,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1108</v>
+        <v>103021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2277,10 +2277,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>861884</v>
+        <v>861880</v>
       </c>
       <c r="R18" t="n">
-        <v>7457456</v>
+        <v>7457458</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2339,10 +2339,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127299628</v>
+        <v>127299640</v>
       </c>
       <c r="B19" t="n">
-        <v>57821</v>
+        <v>91326</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2350,21 +2350,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103021</v>
+        <v>1108</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2374,10 +2374,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>861880</v>
+        <v>861884</v>
       </c>
       <c r="R19" t="n">
-        <v>7457458</v>
+        <v>7457456</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>

--- a/artfynd/A 4107-2022 artfynd.xlsx
+++ b/artfynd/A 4107-2022 artfynd.xlsx
@@ -2242,10 +2242,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127299628</v>
+        <v>127299640</v>
       </c>
       <c r="B18" t="n">
-        <v>57821</v>
+        <v>91326</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2253,21 +2253,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>1108</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2277,10 +2277,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>861880</v>
+        <v>861884</v>
       </c>
       <c r="R18" t="n">
-        <v>7457458</v>
+        <v>7457456</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2339,10 +2339,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127299640</v>
+        <v>127299628</v>
       </c>
       <c r="B19" t="n">
-        <v>91326</v>
+        <v>57821</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2350,21 +2350,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1108</v>
+        <v>103021</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2374,10 +2374,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>861884</v>
+        <v>861880</v>
       </c>
       <c r="R19" t="n">
-        <v>7457456</v>
+        <v>7457458</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>

--- a/artfynd/A 4107-2022 artfynd.xlsx
+++ b/artfynd/A 4107-2022 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127299641</v>
+        <v>127299648</v>
       </c>
       <c r="B3" t="n">
-        <v>91348</v>
+        <v>79020</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,21 +788,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>861760</v>
+        <v>861927</v>
       </c>
       <c r="R3" t="n">
-        <v>7457133</v>
+        <v>7457463</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -874,10 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127299648</v>
+        <v>127299641</v>
       </c>
       <c r="B4" t="n">
-        <v>79018</v>
+        <v>91350</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -885,21 +885,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>861927</v>
+        <v>861760</v>
       </c>
       <c r="R4" t="n">
-        <v>7457463</v>
+        <v>7457133</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -971,32 +971,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127299653</v>
+        <v>127299638</v>
       </c>
       <c r="B5" t="n">
-        <v>5177</v>
+        <v>56846</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100526</v>
+        <v>102612</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>861798</v>
+        <v>861780</v>
       </c>
       <c r="R5" t="n">
-        <v>7457305</v>
+        <v>7457155</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1046,7 +1046,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Gnaggångar och kläckhål</t>
+          <t>Upprörd, varnande</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1073,10 +1073,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127299646</v>
+        <v>127299647</v>
       </c>
       <c r="B6" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1108,10 +1108,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>861776</v>
+        <v>861844</v>
       </c>
       <c r="R6" t="n">
-        <v>7457178</v>
+        <v>7457403</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1173,7 +1173,7 @@
         <v>127299643</v>
       </c>
       <c r="B7" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1267,10 +1267,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127299647</v>
+        <v>127299646</v>
       </c>
       <c r="B8" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1302,10 +1302,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>861844</v>
+        <v>861776</v>
       </c>
       <c r="R8" t="n">
-        <v>7457403</v>
+        <v>7457178</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1364,32 +1364,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127299638</v>
+        <v>127299653</v>
       </c>
       <c r="B9" t="n">
-        <v>56844</v>
+        <v>5177</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102612</v>
+        <v>100526</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1399,10 +1399,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>861780</v>
+        <v>861798</v>
       </c>
       <c r="R9" t="n">
-        <v>7457155</v>
+        <v>7457305</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1439,7 +1439,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Upprörd, varnande</t>
+          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1469,7 +1469,7 @@
         <v>127299622</v>
       </c>
       <c r="B10" t="n">
-        <v>105471</v>
+        <v>105473</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>127299626</v>
       </c>
       <c r="B11" t="n">
-        <v>91295</v>
+        <v>91297</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1663,7 +1663,7 @@
         <v>127299627</v>
       </c>
       <c r="B12" t="n">
-        <v>57821</v>
+        <v>57823</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1760,7 +1760,7 @@
         <v>127299642</v>
       </c>
       <c r="B13" t="n">
-        <v>91348</v>
+        <v>91350</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1857,7 +1857,7 @@
         <v>127299629</v>
       </c>
       <c r="B14" t="n">
-        <v>97325</v>
+        <v>97327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1954,7 +1954,7 @@
         <v>127299649</v>
       </c>
       <c r="B15" t="n">
-        <v>98365</v>
+        <v>98367</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2051,7 +2051,7 @@
         <v>127299644</v>
       </c>
       <c r="B16" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2148,7 +2148,7 @@
         <v>127299625</v>
       </c>
       <c r="B17" t="n">
-        <v>75142</v>
+        <v>75144</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2245,7 +2245,7 @@
         <v>127299640</v>
       </c>
       <c r="B18" t="n">
-        <v>91326</v>
+        <v>91328</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2342,7 +2342,7 @@
         <v>127299628</v>
       </c>
       <c r="B19" t="n">
-        <v>57821</v>
+        <v>57823</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2436,32 +2436,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127299645</v>
+        <v>127299652</v>
       </c>
       <c r="B20" t="n">
-        <v>79018</v>
+        <v>5177</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2471,10 +2471,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>861782</v>
+        <v>861748</v>
       </c>
       <c r="R20" t="n">
-        <v>7457172</v>
+        <v>7457109</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2507,6 +2507,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2533,10 +2538,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127299652</v>
+        <v>127299631</v>
       </c>
       <c r="B21" t="n">
-        <v>5177</v>
+        <v>97327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2544,21 +2549,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100526</v>
+        <v>221945</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2568,10 +2573,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>861748</v>
+        <v>861925</v>
       </c>
       <c r="R21" t="n">
-        <v>7457109</v>
+        <v>7457463</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2604,11 +2609,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2635,32 +2635,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127299631</v>
+        <v>127299645</v>
       </c>
       <c r="B22" t="n">
-        <v>97325</v>
+        <v>79020</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2670,10 +2670,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>861925</v>
+        <v>861782</v>
       </c>
       <c r="R22" t="n">
-        <v>7457463</v>
+        <v>7457172</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>

--- a/artfynd/A 4107-2022 artfynd.xlsx
+++ b/artfynd/A 4107-2022 artfynd.xlsx
@@ -971,10 +971,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127299638</v>
+        <v>127299647</v>
       </c>
       <c r="B5" t="n">
-        <v>56846</v>
+        <v>79020</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -982,21 +982,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>861780</v>
+        <v>861844</v>
       </c>
       <c r="R5" t="n">
-        <v>7457155</v>
+        <v>7457403</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1042,11 +1042,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Upprörd, varnande</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1073,7 +1068,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127299647</v>
+        <v>127299643</v>
       </c>
       <c r="B6" t="n">
         <v>79020</v>
@@ -1108,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>861844</v>
+        <v>861770</v>
       </c>
       <c r="R6" t="n">
-        <v>7457403</v>
+        <v>7457108</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1170,7 +1165,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127299643</v>
+        <v>127299646</v>
       </c>
       <c r="B7" t="n">
         <v>79020</v>
@@ -1205,10 +1200,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>861770</v>
+        <v>861776</v>
       </c>
       <c r="R7" t="n">
-        <v>7457108</v>
+        <v>7457178</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1267,10 +1262,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127299646</v>
+        <v>127299638</v>
       </c>
       <c r="B8" t="n">
-        <v>79020</v>
+        <v>56846</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1278,21 +1273,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1302,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>861776</v>
+        <v>861780</v>
       </c>
       <c r="R8" t="n">
-        <v>7457178</v>
+        <v>7457155</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1338,6 +1333,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Upprörd, varnande</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -2242,10 +2242,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127299640</v>
+        <v>127299628</v>
       </c>
       <c r="B18" t="n">
-        <v>91328</v>
+        <v>57823</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2253,21 +2253,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1108</v>
+        <v>103021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2277,10 +2277,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>861884</v>
+        <v>861880</v>
       </c>
       <c r="R18" t="n">
-        <v>7457456</v>
+        <v>7457458</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2339,10 +2339,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127299628</v>
+        <v>127299640</v>
       </c>
       <c r="B19" t="n">
-        <v>57823</v>
+        <v>91328</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2350,21 +2350,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103021</v>
+        <v>1108</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2374,10 +2374,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>861880</v>
+        <v>861884</v>
       </c>
       <c r="R19" t="n">
-        <v>7457458</v>
+        <v>7457456</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2436,32 +2436,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127299652</v>
+        <v>127299645</v>
       </c>
       <c r="B20" t="n">
-        <v>5177</v>
+        <v>79020</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2471,10 +2471,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>861748</v>
+        <v>861782</v>
       </c>
       <c r="R20" t="n">
-        <v>7457109</v>
+        <v>7457172</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2507,11 +2507,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2538,10 +2533,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127299631</v>
+        <v>127299652</v>
       </c>
       <c r="B21" t="n">
-        <v>97327</v>
+        <v>5177</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2549,21 +2544,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221945</v>
+        <v>100526</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2573,10 +2568,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>861925</v>
+        <v>861748</v>
       </c>
       <c r="R21" t="n">
-        <v>7457463</v>
+        <v>7457109</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2609,6 +2604,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2635,32 +2635,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127299645</v>
+        <v>127299631</v>
       </c>
       <c r="B22" t="n">
-        <v>79020</v>
+        <v>97327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2670,10 +2670,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>861782</v>
+        <v>861925</v>
       </c>
       <c r="R22" t="n">
-        <v>7457172</v>
+        <v>7457463</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>

--- a/artfynd/A 4107-2022 artfynd.xlsx
+++ b/artfynd/A 4107-2022 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127299648</v>
+        <v>127299641</v>
       </c>
       <c r="B3" t="n">
-        <v>79020</v>
+        <v>91350</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,21 +788,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>861927</v>
+        <v>861760</v>
       </c>
       <c r="R3" t="n">
-        <v>7457463</v>
+        <v>7457133</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -874,10 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127299641</v>
+        <v>127299648</v>
       </c>
       <c r="B4" t="n">
-        <v>91350</v>
+        <v>79020</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -885,21 +885,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>861760</v>
+        <v>861927</v>
       </c>
       <c r="R4" t="n">
-        <v>7457133</v>
+        <v>7457463</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1757,32 +1757,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127299642</v>
+        <v>127299629</v>
       </c>
       <c r="B13" t="n">
-        <v>91350</v>
+        <v>97327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>221945</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1792,10 +1792,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>861728</v>
+        <v>861780</v>
       </c>
       <c r="R13" t="n">
-        <v>7457085</v>
+        <v>7457147</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1854,32 +1854,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127299629</v>
+        <v>127299642</v>
       </c>
       <c r="B14" t="n">
-        <v>97327</v>
+        <v>91350</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221945</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1889,10 +1889,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>861780</v>
+        <v>861728</v>
       </c>
       <c r="R14" t="n">
-        <v>7457147</v>
+        <v>7457085</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>

--- a/artfynd/A 4107-2022 artfynd.xlsx
+++ b/artfynd/A 4107-2022 artfynd.xlsx
@@ -971,7 +971,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127299647</v>
+        <v>127299646</v>
       </c>
       <c r="B5" t="n">
         <v>79020</v>
@@ -1006,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>861844</v>
+        <v>861776</v>
       </c>
       <c r="R5" t="n">
-        <v>7457403</v>
+        <v>7457178</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1165,7 +1165,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127299646</v>
+        <v>127299647</v>
       </c>
       <c r="B7" t="n">
         <v>79020</v>
@@ -1200,10 +1200,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>861776</v>
+        <v>861844</v>
       </c>
       <c r="R7" t="n">
-        <v>7457178</v>
+        <v>7457403</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1262,32 +1262,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127299638</v>
+        <v>127299653</v>
       </c>
       <c r="B8" t="n">
-        <v>56846</v>
+        <v>5177</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102612</v>
+        <v>100526</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>861780</v>
+        <v>861798</v>
       </c>
       <c r="R8" t="n">
-        <v>7457155</v>
+        <v>7457305</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Upprörd, varnande</t>
+          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1364,32 +1364,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127299653</v>
+        <v>127299638</v>
       </c>
       <c r="B9" t="n">
-        <v>5177</v>
+        <v>56846</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100526</v>
+        <v>102612</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1399,10 +1399,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>861798</v>
+        <v>861780</v>
       </c>
       <c r="R9" t="n">
-        <v>7457305</v>
+        <v>7457155</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1439,7 +1439,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Gnaggångar och kläckhål</t>
+          <t>Upprörd, varnande</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1563,32 +1563,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127299626</v>
+        <v>127299627</v>
       </c>
       <c r="B11" t="n">
-        <v>91297</v>
+        <v>57823</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5447</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1598,10 +1598,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>861728</v>
+        <v>861840</v>
       </c>
       <c r="R11" t="n">
-        <v>7457083</v>
+        <v>7457419</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1660,32 +1660,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127299627</v>
+        <v>127299626</v>
       </c>
       <c r="B12" t="n">
-        <v>57823</v>
+        <v>91297</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1695,10 +1695,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>861840</v>
+        <v>861728</v>
       </c>
       <c r="R12" t="n">
-        <v>7457419</v>
+        <v>7457083</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -2242,10 +2242,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127299628</v>
+        <v>127299640</v>
       </c>
       <c r="B18" t="n">
-        <v>57823</v>
+        <v>91328</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2253,21 +2253,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>1108</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2277,10 +2277,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>861880</v>
+        <v>861884</v>
       </c>
       <c r="R18" t="n">
-        <v>7457458</v>
+        <v>7457456</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2339,10 +2339,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127299640</v>
+        <v>127299628</v>
       </c>
       <c r="B19" t="n">
-        <v>91328</v>
+        <v>57823</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2350,21 +2350,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1108</v>
+        <v>103021</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2374,10 +2374,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>861884</v>
+        <v>861880</v>
       </c>
       <c r="R19" t="n">
-        <v>7457456</v>
+        <v>7457458</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>

--- a/artfynd/A 4107-2022 artfynd.xlsx
+++ b/artfynd/A 4107-2022 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>127299641</v>
       </c>
       <c r="B3" t="n">
-        <v>91350</v>
+        <v>91356</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
         <v>127299622</v>
       </c>
       <c r="B10" t="n">
-        <v>105473</v>
+        <v>105479</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1563,32 +1563,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127299627</v>
+        <v>127299626</v>
       </c>
       <c r="B11" t="n">
-        <v>57823</v>
+        <v>91303</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>5447</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1598,10 +1598,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>861840</v>
+        <v>861728</v>
       </c>
       <c r="R11" t="n">
-        <v>7457419</v>
+        <v>7457083</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1660,32 +1660,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127299626</v>
+        <v>127299627</v>
       </c>
       <c r="B12" t="n">
-        <v>91297</v>
+        <v>57823</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5447</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1695,10 +1695,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>861728</v>
+        <v>861840</v>
       </c>
       <c r="R12" t="n">
-        <v>7457083</v>
+        <v>7457419</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1760,7 +1760,7 @@
         <v>127299629</v>
       </c>
       <c r="B13" t="n">
-        <v>97327</v>
+        <v>97333</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1857,7 +1857,7 @@
         <v>127299642</v>
       </c>
       <c r="B14" t="n">
-        <v>91350</v>
+        <v>91356</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1954,7 +1954,7 @@
         <v>127299649</v>
       </c>
       <c r="B15" t="n">
-        <v>98367</v>
+        <v>98373</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2245,7 +2245,7 @@
         <v>127299640</v>
       </c>
       <c r="B18" t="n">
-        <v>91328</v>
+        <v>91334</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2436,32 +2436,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127299645</v>
+        <v>127299631</v>
       </c>
       <c r="B20" t="n">
-        <v>79020</v>
+        <v>97333</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2471,10 +2471,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>861782</v>
+        <v>861925</v>
       </c>
       <c r="R20" t="n">
-        <v>7457172</v>
+        <v>7457463</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2635,32 +2635,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127299631</v>
+        <v>127299645</v>
       </c>
       <c r="B22" t="n">
-        <v>97327</v>
+        <v>79020</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2670,10 +2670,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>861925</v>
+        <v>861782</v>
       </c>
       <c r="R22" t="n">
-        <v>7457463</v>
+        <v>7457172</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>

--- a/artfynd/A 4107-2022 artfynd.xlsx
+++ b/artfynd/A 4107-2022 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127299641</v>
+        <v>127299648</v>
       </c>
       <c r="B3" t="n">
-        <v>91356</v>
+        <v>79023</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,21 +788,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>861760</v>
+        <v>861927</v>
       </c>
       <c r="R3" t="n">
-        <v>7457133</v>
+        <v>7457463</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -874,10 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127299648</v>
+        <v>127299641</v>
       </c>
       <c r="B4" t="n">
-        <v>79020</v>
+        <v>91359</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -885,21 +885,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>861927</v>
+        <v>861760</v>
       </c>
       <c r="R4" t="n">
-        <v>7457463</v>
+        <v>7457133</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -971,32 +971,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127299646</v>
+        <v>127299653</v>
       </c>
       <c r="B5" t="n">
-        <v>79020</v>
+        <v>5177</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>861776</v>
+        <v>861798</v>
       </c>
       <c r="R5" t="n">
-        <v>7457178</v>
+        <v>7457305</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1042,6 +1042,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1068,10 +1073,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127299643</v>
+        <v>127299638</v>
       </c>
       <c r="B6" t="n">
-        <v>79020</v>
+        <v>56849</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1079,21 +1084,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1103,10 +1108,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>861770</v>
+        <v>861780</v>
       </c>
       <c r="R6" t="n">
-        <v>7457108</v>
+        <v>7457155</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1139,6 +1144,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Upprörd, varnande</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1165,10 +1175,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127299647</v>
+        <v>127299646</v>
       </c>
       <c r="B7" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1200,10 +1210,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>861844</v>
+        <v>861776</v>
       </c>
       <c r="R7" t="n">
-        <v>7457403</v>
+        <v>7457178</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1262,32 +1272,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127299653</v>
+        <v>127299643</v>
       </c>
       <c r="B8" t="n">
-        <v>5177</v>
+        <v>79023</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1297,10 +1307,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>861798</v>
+        <v>861770</v>
       </c>
       <c r="R8" t="n">
-        <v>7457305</v>
+        <v>7457108</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1333,11 +1343,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1364,10 +1369,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127299638</v>
+        <v>127299647</v>
       </c>
       <c r="B9" t="n">
-        <v>56846</v>
+        <v>79023</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1375,21 +1380,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1399,10 +1404,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>861780</v>
+        <v>861844</v>
       </c>
       <c r="R9" t="n">
-        <v>7457155</v>
+        <v>7457403</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1435,11 +1440,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Upprörd, varnande</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1469,7 +1469,7 @@
         <v>127299622</v>
       </c>
       <c r="B10" t="n">
-        <v>105479</v>
+        <v>105482</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>127299626</v>
       </c>
       <c r="B11" t="n">
-        <v>91303</v>
+        <v>91306</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1663,7 +1663,7 @@
         <v>127299627</v>
       </c>
       <c r="B12" t="n">
-        <v>57823</v>
+        <v>57826</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1757,32 +1757,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127299629</v>
+        <v>127299642</v>
       </c>
       <c r="B13" t="n">
-        <v>97333</v>
+        <v>91359</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221945</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1792,10 +1792,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>861780</v>
+        <v>861728</v>
       </c>
       <c r="R13" t="n">
-        <v>7457147</v>
+        <v>7457085</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1854,32 +1854,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127299642</v>
+        <v>127299629</v>
       </c>
       <c r="B14" t="n">
-        <v>91356</v>
+        <v>97336</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>221945</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1889,10 +1889,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>861728</v>
+        <v>861780</v>
       </c>
       <c r="R14" t="n">
-        <v>7457085</v>
+        <v>7457147</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -1954,7 +1954,7 @@
         <v>127299649</v>
       </c>
       <c r="B15" t="n">
-        <v>98373</v>
+        <v>98376</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2051,7 +2051,7 @@
         <v>127299644</v>
       </c>
       <c r="B16" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2148,7 +2148,7 @@
         <v>127299625</v>
       </c>
       <c r="B17" t="n">
-        <v>75144</v>
+        <v>75147</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2245,7 +2245,7 @@
         <v>127299640</v>
       </c>
       <c r="B18" t="n">
-        <v>91334</v>
+        <v>91337</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2342,7 +2342,7 @@
         <v>127299628</v>
       </c>
       <c r="B19" t="n">
-        <v>57823</v>
+        <v>57826</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2436,10 +2436,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127299631</v>
+        <v>127299652</v>
       </c>
       <c r="B20" t="n">
-        <v>97333</v>
+        <v>5177</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2447,21 +2447,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221945</v>
+        <v>100526</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2471,10 +2471,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>861925</v>
+        <v>861748</v>
       </c>
       <c r="R20" t="n">
-        <v>7457463</v>
+        <v>7457109</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2507,6 +2507,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2533,32 +2538,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127299652</v>
+        <v>127299645</v>
       </c>
       <c r="B21" t="n">
-        <v>5177</v>
+        <v>79023</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2568,10 +2573,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>861748</v>
+        <v>861782</v>
       </c>
       <c r="R21" t="n">
-        <v>7457109</v>
+        <v>7457172</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2604,11 +2609,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2635,32 +2635,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127299645</v>
+        <v>127299631</v>
       </c>
       <c r="B22" t="n">
-        <v>79020</v>
+        <v>97336</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2670,10 +2670,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>861782</v>
+        <v>861925</v>
       </c>
       <c r="R22" t="n">
-        <v>7457172</v>
+        <v>7457463</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>

--- a/artfynd/A 4107-2022 artfynd.xlsx
+++ b/artfynd/A 4107-2022 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127299648</v>
+        <v>127299641</v>
       </c>
       <c r="B3" t="n">
-        <v>79023</v>
+        <v>91367</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,21 +788,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>861927</v>
+        <v>861760</v>
       </c>
       <c r="R3" t="n">
-        <v>7457463</v>
+        <v>7457133</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -874,10 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127299641</v>
+        <v>127299648</v>
       </c>
       <c r="B4" t="n">
-        <v>91359</v>
+        <v>79029</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -885,21 +885,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>861760</v>
+        <v>861927</v>
       </c>
       <c r="R4" t="n">
-        <v>7457133</v>
+        <v>7457463</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -971,32 +971,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127299653</v>
+        <v>127299647</v>
       </c>
       <c r="B5" t="n">
-        <v>5177</v>
+        <v>79029</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>861798</v>
+        <v>861844</v>
       </c>
       <c r="R5" t="n">
-        <v>7457305</v>
+        <v>7457403</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1042,11 +1042,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1073,10 +1068,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127299638</v>
+        <v>127299643</v>
       </c>
       <c r="B6" t="n">
-        <v>56849</v>
+        <v>79029</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1084,21 +1079,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1108,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>861780</v>
+        <v>861770</v>
       </c>
       <c r="R6" t="n">
-        <v>7457155</v>
+        <v>7457108</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1144,11 +1139,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Upprörd, varnande</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1178,7 +1168,7 @@
         <v>127299646</v>
       </c>
       <c r="B7" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1272,32 +1262,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127299643</v>
+        <v>127299653</v>
       </c>
       <c r="B8" t="n">
-        <v>79023</v>
+        <v>5177</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1307,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>861770</v>
+        <v>861798</v>
       </c>
       <c r="R8" t="n">
-        <v>7457108</v>
+        <v>7457305</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1343,6 +1333,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1369,10 +1364,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127299647</v>
+        <v>127299638</v>
       </c>
       <c r="B9" t="n">
-        <v>79023</v>
+        <v>56855</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1380,21 +1375,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1404,10 +1399,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>861844</v>
+        <v>861780</v>
       </c>
       <c r="R9" t="n">
-        <v>7457403</v>
+        <v>7457155</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1440,6 +1435,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Upprörd, varnande</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1469,7 +1469,7 @@
         <v>127299622</v>
       </c>
       <c r="B10" t="n">
-        <v>105482</v>
+        <v>105490</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>127299626</v>
       </c>
       <c r="B11" t="n">
-        <v>91306</v>
+        <v>91314</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1663,7 +1663,7 @@
         <v>127299627</v>
       </c>
       <c r="B12" t="n">
-        <v>57826</v>
+        <v>57832</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1757,32 +1757,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127299642</v>
+        <v>127299629</v>
       </c>
       <c r="B13" t="n">
-        <v>91359</v>
+        <v>97344</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>221945</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1792,10 +1792,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>861728</v>
+        <v>861780</v>
       </c>
       <c r="R13" t="n">
-        <v>7457085</v>
+        <v>7457147</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1854,32 +1854,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127299629</v>
+        <v>127299642</v>
       </c>
       <c r="B14" t="n">
-        <v>97336</v>
+        <v>91367</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221945</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1889,10 +1889,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>861780</v>
+        <v>861728</v>
       </c>
       <c r="R14" t="n">
-        <v>7457147</v>
+        <v>7457085</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -1954,7 +1954,7 @@
         <v>127299649</v>
       </c>
       <c r="B15" t="n">
-        <v>98376</v>
+        <v>98384</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2051,7 +2051,7 @@
         <v>127299644</v>
       </c>
       <c r="B16" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2148,7 +2148,7 @@
         <v>127299625</v>
       </c>
       <c r="B17" t="n">
-        <v>75147</v>
+        <v>75153</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2245,7 +2245,7 @@
         <v>127299640</v>
       </c>
       <c r="B18" t="n">
-        <v>91337</v>
+        <v>91345</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2342,7 +2342,7 @@
         <v>127299628</v>
       </c>
       <c r="B19" t="n">
-        <v>57826</v>
+        <v>57832</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2538,32 +2538,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127299645</v>
+        <v>127299631</v>
       </c>
       <c r="B21" t="n">
-        <v>79023</v>
+        <v>97344</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2573,10 +2573,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>861782</v>
+        <v>861925</v>
       </c>
       <c r="R21" t="n">
-        <v>7457172</v>
+        <v>7457463</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2635,32 +2635,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127299631</v>
+        <v>127299645</v>
       </c>
       <c r="B22" t="n">
-        <v>97336</v>
+        <v>79029</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2670,10 +2670,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>861925</v>
+        <v>861782</v>
       </c>
       <c r="R22" t="n">
-        <v>7457463</v>
+        <v>7457172</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>

--- a/artfynd/A 4107-2022 artfynd.xlsx
+++ b/artfynd/A 4107-2022 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>127299641</v>
       </c>
       <c r="B3" t="n">
-        <v>91367</v>
+        <v>91368</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -971,32 +971,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127299647</v>
+        <v>127299653</v>
       </c>
       <c r="B5" t="n">
-        <v>79029</v>
+        <v>5177</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>861844</v>
+        <v>861798</v>
       </c>
       <c r="R5" t="n">
-        <v>7457403</v>
+        <v>7457305</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1042,6 +1042,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1068,10 +1073,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127299643</v>
+        <v>127299638</v>
       </c>
       <c r="B6" t="n">
-        <v>79029</v>
+        <v>56855</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1079,21 +1084,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1103,10 +1108,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>861770</v>
+        <v>861780</v>
       </c>
       <c r="R6" t="n">
-        <v>7457108</v>
+        <v>7457155</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1139,6 +1144,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Upprörd, varnande</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1262,32 +1272,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127299653</v>
+        <v>127299643</v>
       </c>
       <c r="B8" t="n">
-        <v>5177</v>
+        <v>79029</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1297,10 +1307,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>861798</v>
+        <v>861770</v>
       </c>
       <c r="R8" t="n">
-        <v>7457305</v>
+        <v>7457108</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1333,11 +1343,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1364,10 +1369,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127299638</v>
+        <v>127299647</v>
       </c>
       <c r="B9" t="n">
-        <v>56855</v>
+        <v>79029</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1375,21 +1380,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1399,10 +1404,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>861780</v>
+        <v>861844</v>
       </c>
       <c r="R9" t="n">
-        <v>7457155</v>
+        <v>7457403</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1435,11 +1440,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Upprörd, varnande</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1469,7 +1469,7 @@
         <v>127299622</v>
       </c>
       <c r="B10" t="n">
-        <v>105490</v>
+        <v>105491</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>127299626</v>
       </c>
       <c r="B11" t="n">
-        <v>91314</v>
+        <v>91315</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1757,32 +1757,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127299629</v>
+        <v>127299642</v>
       </c>
       <c r="B13" t="n">
-        <v>97344</v>
+        <v>91368</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221945</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1792,10 +1792,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>861780</v>
+        <v>861728</v>
       </c>
       <c r="R13" t="n">
-        <v>7457147</v>
+        <v>7457085</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1854,32 +1854,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127299642</v>
+        <v>127299629</v>
       </c>
       <c r="B14" t="n">
-        <v>91367</v>
+        <v>97345</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>221945</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1889,10 +1889,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>861728</v>
+        <v>861780</v>
       </c>
       <c r="R14" t="n">
-        <v>7457085</v>
+        <v>7457147</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -1954,7 +1954,7 @@
         <v>127299649</v>
       </c>
       <c r="B15" t="n">
-        <v>98384</v>
+        <v>98385</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2245,7 +2245,7 @@
         <v>127299640</v>
       </c>
       <c r="B18" t="n">
-        <v>91345</v>
+        <v>91346</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2541,7 +2541,7 @@
         <v>127299631</v>
       </c>
       <c r="B21" t="n">
-        <v>97344</v>
+        <v>97345</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 4107-2022 artfynd.xlsx
+++ b/artfynd/A 4107-2022 artfynd.xlsx
@@ -971,32 +971,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127299653</v>
+        <v>127299646</v>
       </c>
       <c r="B5" t="n">
-        <v>5177</v>
+        <v>79029</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>861798</v>
+        <v>861776</v>
       </c>
       <c r="R5" t="n">
-        <v>7457305</v>
+        <v>7457178</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1042,11 +1042,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1073,10 +1068,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127299638</v>
+        <v>127299643</v>
       </c>
       <c r="B6" t="n">
-        <v>56855</v>
+        <v>79029</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1084,21 +1079,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1108,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>861780</v>
+        <v>861770</v>
       </c>
       <c r="R6" t="n">
-        <v>7457155</v>
+        <v>7457108</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1144,11 +1139,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Upprörd, varnande</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1175,7 +1165,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127299646</v>
+        <v>127299647</v>
       </c>
       <c r="B7" t="n">
         <v>79029</v>
@@ -1210,10 +1200,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>861776</v>
+        <v>861844</v>
       </c>
       <c r="R7" t="n">
-        <v>7457178</v>
+        <v>7457403</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1272,10 +1262,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127299643</v>
+        <v>127299638</v>
       </c>
       <c r="B8" t="n">
-        <v>79029</v>
+        <v>56855</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1283,21 +1273,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1307,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>861770</v>
+        <v>861780</v>
       </c>
       <c r="R8" t="n">
-        <v>7457108</v>
+        <v>7457155</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1343,6 +1333,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Upprörd, varnande</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1369,32 +1364,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127299647</v>
+        <v>127299653</v>
       </c>
       <c r="B9" t="n">
-        <v>79029</v>
+        <v>5177</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1404,10 +1399,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>861844</v>
+        <v>861798</v>
       </c>
       <c r="R9" t="n">
-        <v>7457403</v>
+        <v>7457305</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1440,6 +1435,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1563,32 +1563,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127299626</v>
+        <v>127299627</v>
       </c>
       <c r="B11" t="n">
-        <v>91315</v>
+        <v>57832</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5447</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1598,10 +1598,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>861728</v>
+        <v>861840</v>
       </c>
       <c r="R11" t="n">
-        <v>7457083</v>
+        <v>7457419</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1660,32 +1660,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127299627</v>
+        <v>127299626</v>
       </c>
       <c r="B12" t="n">
-        <v>57832</v>
+        <v>91315</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1695,10 +1695,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>861840</v>
+        <v>861728</v>
       </c>
       <c r="R12" t="n">
-        <v>7457419</v>
+        <v>7457083</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1757,32 +1757,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127299642</v>
+        <v>127299629</v>
       </c>
       <c r="B13" t="n">
-        <v>91368</v>
+        <v>97345</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>221945</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1792,10 +1792,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>861728</v>
+        <v>861780</v>
       </c>
       <c r="R13" t="n">
-        <v>7457085</v>
+        <v>7457147</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1854,32 +1854,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127299629</v>
+        <v>127299642</v>
       </c>
       <c r="B14" t="n">
-        <v>97345</v>
+        <v>91368</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221945</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1889,10 +1889,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>861780</v>
+        <v>861728</v>
       </c>
       <c r="R14" t="n">
-        <v>7457147</v>
+        <v>7457085</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2436,32 +2436,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127299652</v>
+        <v>127299645</v>
       </c>
       <c r="B20" t="n">
-        <v>5177</v>
+        <v>79029</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2471,10 +2471,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>861748</v>
+        <v>861782</v>
       </c>
       <c r="R20" t="n">
-        <v>7457109</v>
+        <v>7457172</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2507,11 +2507,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2538,10 +2533,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127299631</v>
+        <v>127299652</v>
       </c>
       <c r="B21" t="n">
-        <v>97345</v>
+        <v>5177</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2549,21 +2544,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221945</v>
+        <v>100526</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2573,10 +2568,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>861925</v>
+        <v>861748</v>
       </c>
       <c r="R21" t="n">
-        <v>7457463</v>
+        <v>7457109</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2609,6 +2604,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2635,32 +2635,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127299645</v>
+        <v>127299631</v>
       </c>
       <c r="B22" t="n">
-        <v>79029</v>
+        <v>97345</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2670,10 +2670,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>861782</v>
+        <v>861925</v>
       </c>
       <c r="R22" t="n">
-        <v>7457172</v>
+        <v>7457463</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>

--- a/artfynd/A 4107-2022 artfynd.xlsx
+++ b/artfynd/A 4107-2022 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>127299641</v>
       </c>
       <c r="B3" t="n">
-        <v>91368</v>
+        <v>91369</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -971,10 +971,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127299646</v>
+        <v>127299638</v>
       </c>
       <c r="B5" t="n">
-        <v>79029</v>
+        <v>56855</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -982,21 +982,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>861776</v>
+        <v>861780</v>
       </c>
       <c r="R5" t="n">
-        <v>7457178</v>
+        <v>7457155</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1042,6 +1042,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Upprörd, varnande</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1068,7 +1073,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127299643</v>
+        <v>127299647</v>
       </c>
       <c r="B6" t="n">
         <v>79029</v>
@@ -1103,10 +1108,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>861770</v>
+        <v>861844</v>
       </c>
       <c r="R6" t="n">
-        <v>7457108</v>
+        <v>7457403</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1165,32 +1170,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127299647</v>
+        <v>127299653</v>
       </c>
       <c r="B7" t="n">
-        <v>79029</v>
+        <v>5177</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1200,10 +1205,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>861844</v>
+        <v>861798</v>
       </c>
       <c r="R7" t="n">
-        <v>7457403</v>
+        <v>7457305</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1236,6 +1241,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1262,10 +1272,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127299638</v>
+        <v>127299646</v>
       </c>
       <c r="B8" t="n">
-        <v>56855</v>
+        <v>79029</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1273,21 +1283,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1297,10 +1307,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>861780</v>
+        <v>861776</v>
       </c>
       <c r="R8" t="n">
-        <v>7457155</v>
+        <v>7457178</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1333,11 +1343,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Upprörd, varnande</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1364,32 +1369,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127299653</v>
+        <v>127299643</v>
       </c>
       <c r="B9" t="n">
-        <v>5177</v>
+        <v>79029</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1399,10 +1404,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>861798</v>
+        <v>861770</v>
       </c>
       <c r="R9" t="n">
-        <v>7457305</v>
+        <v>7457108</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1435,11 +1440,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1469,7 +1469,7 @@
         <v>127299622</v>
       </c>
       <c r="B10" t="n">
-        <v>105491</v>
+        <v>105492</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1563,32 +1563,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127299627</v>
+        <v>127299626</v>
       </c>
       <c r="B11" t="n">
-        <v>57832</v>
+        <v>91316</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>5447</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1598,10 +1598,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>861840</v>
+        <v>861728</v>
       </c>
       <c r="R11" t="n">
-        <v>7457419</v>
+        <v>7457083</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1660,32 +1660,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127299626</v>
+        <v>127299627</v>
       </c>
       <c r="B12" t="n">
-        <v>91315</v>
+        <v>57832</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5447</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1695,10 +1695,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>861728</v>
+        <v>861840</v>
       </c>
       <c r="R12" t="n">
-        <v>7457083</v>
+        <v>7457419</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1757,32 +1757,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127299629</v>
+        <v>127299642</v>
       </c>
       <c r="B13" t="n">
-        <v>97345</v>
+        <v>91369</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221945</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1792,10 +1792,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>861780</v>
+        <v>861728</v>
       </c>
       <c r="R13" t="n">
-        <v>7457147</v>
+        <v>7457085</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1854,32 +1854,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127299642</v>
+        <v>127299629</v>
       </c>
       <c r="B14" t="n">
-        <v>91368</v>
+        <v>97346</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>221945</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1889,10 +1889,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>861728</v>
+        <v>861780</v>
       </c>
       <c r="R14" t="n">
-        <v>7457085</v>
+        <v>7457147</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -1954,7 +1954,7 @@
         <v>127299649</v>
       </c>
       <c r="B15" t="n">
-        <v>98385</v>
+        <v>98386</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2245,7 +2245,7 @@
         <v>127299640</v>
       </c>
       <c r="B18" t="n">
-        <v>91346</v>
+        <v>91347</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2436,32 +2436,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127299645</v>
+        <v>127299631</v>
       </c>
       <c r="B20" t="n">
-        <v>79029</v>
+        <v>97346</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2471,10 +2471,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>861782</v>
+        <v>861925</v>
       </c>
       <c r="R20" t="n">
-        <v>7457172</v>
+        <v>7457463</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2635,32 +2635,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127299631</v>
+        <v>127299645</v>
       </c>
       <c r="B22" t="n">
-        <v>97345</v>
+        <v>79029</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2670,10 +2670,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>861925</v>
+        <v>861782</v>
       </c>
       <c r="R22" t="n">
-        <v>7457463</v>
+        <v>7457172</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>

--- a/artfynd/A 4107-2022 artfynd.xlsx
+++ b/artfynd/A 4107-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127299623</v>
       </c>
       <c r="B2" t="n">
-        <v>5197</v>
+        <v>5196</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>127299641</v>
       </c>
       <c r="B3" t="n">
-        <v>91369</v>
+        <v>91337</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>127299648</v>
       </c>
       <c r="B4" t="n">
-        <v>79029</v>
+        <v>79011</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -971,32 +971,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127299638</v>
+        <v>127299653</v>
       </c>
       <c r="B5" t="n">
-        <v>56855</v>
+        <v>5176</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102612</v>
+        <v>100526</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>861780</v>
+        <v>861798</v>
       </c>
       <c r="R5" t="n">
-        <v>7457155</v>
+        <v>7457305</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1046,7 +1046,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Upprörd, varnande</t>
+          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1073,10 +1073,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127299647</v>
+        <v>127299646</v>
       </c>
       <c r="B6" t="n">
-        <v>79029</v>
+        <v>79011</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1108,10 +1108,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>861844</v>
+        <v>861776</v>
       </c>
       <c r="R6" t="n">
-        <v>7457403</v>
+        <v>7457178</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1170,32 +1170,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127299653</v>
+        <v>127299643</v>
       </c>
       <c r="B7" t="n">
-        <v>5177</v>
+        <v>79011</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1205,10 +1205,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>861798</v>
+        <v>861770</v>
       </c>
       <c r="R7" t="n">
-        <v>7457305</v>
+        <v>7457108</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1241,11 +1241,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1272,10 +1267,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127299646</v>
+        <v>127299647</v>
       </c>
       <c r="B8" t="n">
-        <v>79029</v>
+        <v>79011</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1307,10 +1302,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>861776</v>
+        <v>861844</v>
       </c>
       <c r="R8" t="n">
-        <v>7457178</v>
+        <v>7457403</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1369,10 +1364,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127299643</v>
+        <v>127299638</v>
       </c>
       <c r="B9" t="n">
-        <v>79029</v>
+        <v>56840</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1380,21 +1375,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1404,10 +1399,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>861770</v>
+        <v>861780</v>
       </c>
       <c r="R9" t="n">
-        <v>7457108</v>
+        <v>7457155</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1440,6 +1435,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Upprörd, varnande</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1469,7 +1469,7 @@
         <v>127299622</v>
       </c>
       <c r="B10" t="n">
-        <v>105492</v>
+        <v>105456</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>127299626</v>
       </c>
       <c r="B11" t="n">
-        <v>91316</v>
+        <v>91284</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1663,7 +1663,7 @@
         <v>127299627</v>
       </c>
       <c r="B12" t="n">
-        <v>57832</v>
+        <v>57817</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1760,7 +1760,7 @@
         <v>127299642</v>
       </c>
       <c r="B13" t="n">
-        <v>91369</v>
+        <v>91337</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1857,7 +1857,7 @@
         <v>127299629</v>
       </c>
       <c r="B14" t="n">
-        <v>97346</v>
+        <v>97314</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1954,7 +1954,7 @@
         <v>127299649</v>
       </c>
       <c r="B15" t="n">
-        <v>98386</v>
+        <v>98353</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2051,7 +2051,7 @@
         <v>127299644</v>
       </c>
       <c r="B16" t="n">
-        <v>79029</v>
+        <v>79011</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2148,7 +2148,7 @@
         <v>127299625</v>
       </c>
       <c r="B17" t="n">
-        <v>75153</v>
+        <v>75135</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2245,7 +2245,7 @@
         <v>127299640</v>
       </c>
       <c r="B18" t="n">
-        <v>91347</v>
+        <v>91315</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2342,7 +2342,7 @@
         <v>127299628</v>
       </c>
       <c r="B19" t="n">
-        <v>57832</v>
+        <v>57817</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2439,7 +2439,7 @@
         <v>127299631</v>
       </c>
       <c r="B20" t="n">
-        <v>97346</v>
+        <v>97314</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2533,32 +2533,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127299652</v>
+        <v>127299645</v>
       </c>
       <c r="B21" t="n">
-        <v>5177</v>
+        <v>79011</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2568,10 +2568,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>861748</v>
+        <v>861782</v>
       </c>
       <c r="R21" t="n">
-        <v>7457109</v>
+        <v>7457172</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2604,11 +2604,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2635,32 +2630,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127299645</v>
+        <v>127299652</v>
       </c>
       <c r="B22" t="n">
-        <v>79029</v>
+        <v>5176</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2670,10 +2665,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>861782</v>
+        <v>861748</v>
       </c>
       <c r="R22" t="n">
-        <v>7457172</v>
+        <v>7457109</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2706,6 +2701,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD22" t="b">

--- a/artfynd/A 4107-2022 artfynd.xlsx
+++ b/artfynd/A 4107-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:AY21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127299623</v>
+        <v>127299640</v>
       </c>
       <c r="B2" t="n">
-        <v>5197</v>
+        <v>91905</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>105930</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>861800</v>
+        <v>861884</v>
       </c>
       <c r="R2" t="n">
-        <v>7457306</v>
+        <v>7457456</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -746,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127299641</v>
+        <v>127299626</v>
       </c>
       <c r="B3" t="n">
-        <v>91369</v>
+        <v>91872</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>861760</v>
+        <v>861728</v>
       </c>
       <c r="R3" t="n">
-        <v>7457133</v>
+        <v>7457083</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -874,14 +869,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127299648</v>
+        <v>127299643</v>
       </c>
       <c r="B4" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -909,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>861927</v>
+        <v>861770</v>
       </c>
       <c r="R4" t="n">
-        <v>7457463</v>
+        <v>7457108</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -971,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127299638</v>
+        <v>127299644</v>
       </c>
       <c r="B5" t="n">
-        <v>56855</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>861780</v>
+        <v>861741</v>
       </c>
       <c r="R5" t="n">
-        <v>7457155</v>
+        <v>7457113</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1042,11 +1037,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Upprörd, varnande</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1073,14 +1063,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127299647</v>
+        <v>127299645</v>
       </c>
       <c r="B6" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1108,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>861844</v>
+        <v>861782</v>
       </c>
       <c r="R6" t="n">
-        <v>7457403</v>
+        <v>7457172</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1170,32 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127299653</v>
+        <v>127299646</v>
       </c>
       <c r="B7" t="n">
-        <v>5177</v>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1205,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>861798</v>
+        <v>861776</v>
       </c>
       <c r="R7" t="n">
-        <v>7457305</v>
+        <v>7457178</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1241,11 +1231,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1272,14 +1257,14 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127299646</v>
+        <v>127299647</v>
       </c>
       <c r="B8" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1307,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>861776</v>
+        <v>861844</v>
       </c>
       <c r="R8" t="n">
-        <v>7457178</v>
+        <v>7457403</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1369,14 +1354,14 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127299643</v>
+        <v>127299648</v>
       </c>
       <c r="B9" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1404,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>861770</v>
+        <v>861927</v>
       </c>
       <c r="R9" t="n">
-        <v>7457108</v>
+        <v>7457463</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1466,32 +1451,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127299622</v>
+        <v>127299624</v>
       </c>
       <c r="B10" t="n">
-        <v>105492</v>
+        <v>83307</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221725</v>
+        <v>6440</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1501,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>861891</v>
+        <v>861772</v>
       </c>
       <c r="R10" t="n">
-        <v>7457463</v>
+        <v>7457097</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1563,32 +1548,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127299626</v>
+        <v>127299625</v>
       </c>
       <c r="B11" t="n">
-        <v>91316</v>
+        <v>83307</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5447</v>
+        <v>6440</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1598,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>861728</v>
+        <v>861758</v>
       </c>
       <c r="R11" t="n">
-        <v>7457083</v>
+        <v>7457118</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1660,32 +1645,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127299627</v>
+        <v>127299652</v>
       </c>
       <c r="B12" t="n">
-        <v>57832</v>
+        <v>5179</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>100526</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1695,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>861840</v>
+        <v>861748</v>
       </c>
       <c r="R12" t="n">
-        <v>7457419</v>
+        <v>7457109</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1731,6 +1716,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1757,32 +1747,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127299642</v>
+        <v>127299653</v>
       </c>
       <c r="B13" t="n">
-        <v>91369</v>
+        <v>5179</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>100526</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1792,10 +1782,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>861728</v>
+        <v>861798</v>
       </c>
       <c r="R13" t="n">
-        <v>7457085</v>
+        <v>7457305</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1828,6 +1818,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1854,10 +1849,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127299629</v>
+        <v>127299638</v>
       </c>
       <c r="B14" t="n">
-        <v>97346</v>
+        <v>57132</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1865,21 +1860,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221945</v>
+        <v>102612</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1892,7 +1887,7 @@
         <v>861780</v>
       </c>
       <c r="R14" t="n">
-        <v>7457147</v>
+        <v>7457155</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -1925,6 +1920,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Upprörd, varnande</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1951,32 +1951,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127299649</v>
+        <v>127299627</v>
       </c>
       <c r="B15" t="n">
-        <v>98386</v>
+        <v>58114</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219790</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1986,10 +1986,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>861645</v>
+        <v>861840</v>
       </c>
       <c r="R15" t="n">
-        <v>7456997</v>
+        <v>7457419</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2048,10 +2048,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127299644</v>
+        <v>127299628</v>
       </c>
       <c r="B16" t="n">
-        <v>79029</v>
+        <v>58114</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2059,21 +2059,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2083,10 +2083,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>861741</v>
+        <v>861880</v>
       </c>
       <c r="R16" t="n">
-        <v>7457113</v>
+        <v>7457458</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2145,32 +2145,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127299625</v>
+        <v>127299623</v>
       </c>
       <c r="B17" t="n">
-        <v>75153</v>
+        <v>5199</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6440</v>
+        <v>105930</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2180,10 +2180,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>861758</v>
+        <v>861800</v>
       </c>
       <c r="R17" t="n">
-        <v>7457118</v>
+        <v>7457306</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2216,6 +2216,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2242,32 +2247,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127299640</v>
+        <v>127299649</v>
       </c>
       <c r="B18" t="n">
-        <v>91347</v>
+        <v>99035</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1108</v>
+        <v>219790</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2277,10 +2282,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>861884</v>
+        <v>861645</v>
       </c>
       <c r="R18" t="n">
-        <v>7457456</v>
+        <v>7456997</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2339,32 +2344,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127299628</v>
+        <v>127299622</v>
       </c>
       <c r="B19" t="n">
-        <v>57832</v>
+        <v>106229</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103021</v>
+        <v>221725</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2374,10 +2379,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>861880</v>
+        <v>861891</v>
       </c>
       <c r="R19" t="n">
-        <v>7457458</v>
+        <v>7457463</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2436,10 +2441,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127299631</v>
+        <v>127299629</v>
       </c>
       <c r="B20" t="n">
-        <v>97346</v>
+        <v>97983</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2471,10 +2476,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>861925</v>
+        <v>861780</v>
       </c>
       <c r="R20" t="n">
-        <v>7457463</v>
+        <v>7457147</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2533,10 +2538,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127299652</v>
+        <v>127299631</v>
       </c>
       <c r="B21" t="n">
-        <v>5177</v>
+        <v>97983</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2544,21 +2549,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100526</v>
+        <v>221945</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2568,10 +2573,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>861748</v>
+        <v>861925</v>
       </c>
       <c r="R21" t="n">
-        <v>7457109</v>
+        <v>7457463</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2606,11 +2611,6 @@
           <t>2025-08-07</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Gnaggångar och kläckhål</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -2632,103 +2632,6 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>127299645</v>
-      </c>
-      <c r="B22" t="n">
-        <v>79029</v>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E22" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>Isokero, Nb</t>
-        </is>
-      </c>
-      <c r="Q22" t="n">
-        <v>861782</v>
-      </c>
-      <c r="R22" t="n">
-        <v>7457172</v>
-      </c>
-      <c r="S22" t="n">
-        <v>25</v>
-      </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U22" t="inlineStr">
-        <is>
-          <t>Pajala</t>
-        </is>
-      </c>
-      <c r="V22" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>Pajala</t>
-        </is>
-      </c>
-      <c r="Y22" t="inlineStr">
-        <is>
-          <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AA22" t="inlineStr">
-        <is>
-          <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AD22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT22" t="inlineStr"/>
-      <c r="AW22" t="inlineStr">
-        <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY22" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 4107-2022 artfynd.xlsx
+++ b/artfynd/A 4107-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AZ21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127299640</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127299626</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127299643</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127299644</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127299645</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127299646</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127299647</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127299648</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127299624</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127299625</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1744,6 +1799,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127299652</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1846,6 +1906,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127299653</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1948,6 +2013,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127299638</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2045,6 +2115,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127299627</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2142,6 +2217,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127299628</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2244,6 +2324,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127299623</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2341,6 +2426,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127299649</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2438,6 +2528,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127299622</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2535,6 +2630,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127299629</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2632,8 +2732,35 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127299631</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>